--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45675</v>
+        <v>63259</v>
       </c>
     </row>
     <row r="3">

--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>63259</v>
+        <v>9565</v>
       </c>
     </row>
     <row r="3">

--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9565</v>
+        <v>37557</v>
       </c>
     </row>
     <row r="3">

--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37557</v>
+        <v>27579</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -717,7 +717,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -725,7 +725,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -733,7 +733,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -741,7 +741,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -749,7 +749,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -757,7 +757,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -765,7 +765,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -773,7 +773,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -781,7 +781,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -789,7 +789,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -805,7 +805,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -829,7 +829,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -837,7 +837,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -845,7 +845,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -853,7 +853,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -861,7 +861,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -869,7 +869,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -885,7 +885,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -893,7 +893,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -901,7 +901,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -909,7 +909,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -917,7 +917,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -925,7 +925,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -933,7 +933,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -941,7 +941,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -949,7 +949,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -957,7 +957,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -965,7 +965,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -981,7 +981,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -989,7 +989,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -997,7 +997,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1005,7 +1005,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1013,7 +1013,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1021,7 +1021,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1029,7 +1029,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -1037,7 +1037,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1045,7 +1045,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1053,7 +1053,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1061,7 +1061,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1069,7 +1069,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1077,7 +1077,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1093,7 +1093,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1109,7 +1109,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1117,7 +1117,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1125,7 +1125,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1133,7 +1133,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1141,7 +1141,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1149,7 +1149,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1157,7 +1157,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1165,7 +1165,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1173,7 +1173,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1189,7 +1189,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1205,7 +1205,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1213,7 +1213,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -1221,7 +1221,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1229,7 +1229,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1269,7 +1269,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1293,7 +1293,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1301,7 +1301,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1317,7 +1317,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1325,7 +1325,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1341,7 +1341,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -1357,7 +1357,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1405,7 +1405,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1461,7 +1461,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -1469,7 +1469,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -1629,7 +1629,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -1717,7 +1717,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -1749,7 +1749,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -2749,7 +2749,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -2861,7 +2861,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -3413,7 +3413,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -4877,7 +4877,7 @@
         <v>554</v>
       </c>
       <c r="B556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -5269,7 +5269,7 @@
         <v>603</v>
       </c>
       <c r="B605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
@@ -5309,7 +5309,7 @@
         <v>608</v>
       </c>
       <c r="B610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
@@ -6357,7 +6357,7 @@
         <v>739</v>
       </c>
       <c r="B741" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742">
@@ -6389,7 +6389,7 @@
         <v>743</v>
       </c>
       <c r="B745" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="746">
@@ -6469,7 +6469,7 @@
         <v>753</v>
       </c>
       <c r="B755" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="756">

--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -653,7 +653,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -717,7 +717,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -797,7 +797,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -821,7 +821,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -885,7 +885,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1029,7 +1029,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1037,7 +1037,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1469,7 +1469,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1717,7 +1717,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -2861,7 +2861,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -5269,7 +5269,7 @@
         <v>603</v>
       </c>
       <c r="B605" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606">
@@ -5309,7 +5309,7 @@
         <v>608</v>
       </c>
       <c r="B610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -6389,7 +6389,7 @@
         <v>743</v>
       </c>
       <c r="B745" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -6469,7 +6469,7 @@
         <v>753</v>
       </c>
       <c r="B755" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="756">

--- a/spectrum_data.xlsx
+++ b/spectrum_data.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6605</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -677,7 +677,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -989,7 +989,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -1269,7 +1269,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2917,7 +2917,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
